--- a/etf_holdings/2026-08-31_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00403A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M51"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.02%11,100,000</t>
+          <t>16.22%11,000,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.02%</t>
+          <t>16.22%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11100000</v>
+        <v>11000000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.6%3360</t>
+          <t>+1.93%3425</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3360</v>
+        <v>3425</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.31%3,150,000</t>
+          <t>6.62%3,150,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.31%</t>
+          <t>6.62%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.93%1110</t>
+          <t>-0.09%5485</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.93%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1110</v>
+        <v>5485</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.60%8,460,000</t>
+          <t>5.38%1,600,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.38%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8460000</v>
+        <v>1600000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>-10%999</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5490</v>
+        <v>999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.24%1,600,000</t>
+          <t>5.18%8,460,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.24%</t>
+          <t>5.18%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1600000</v>
+        <v>8460000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>-1.51%3925</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3985</v>
+        <v>3925</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.01%2,110,000</t>
+          <t>5.08%2,110,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>5.08%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.7%130</t>
+          <t>+3.54%5990</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>130</v>
+        <v>5990</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.88%50,000,000</t>
+          <t>4.10%1,115,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.88%</t>
+          <t>4.10%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>50000000</v>
+        <v>1115000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.48%5785</t>
+          <t>-0.77%129</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5785</v>
+        <v>129</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.75%1,087,000</t>
+          <t>3.96%50,000,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>3.96%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1087000</v>
+        <v>50000000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+7.57%597</t>
+          <t>+8.28%7650</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+7.57%</t>
+          <t>+8.28%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>597</v>
+        <v>7650</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.48%9,785,000</t>
+          <t>3.80%810,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.48%</t>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>9785000</v>
+        <v>810000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+1.99%5130</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5030</v>
+        <v>5130</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.30%1,100,000</t>
+          <t>3.46%1,100,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.30%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+2.17%7065</t>
+          <t>-8.71%545</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-8.71%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7065</v>
+        <v>545</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.20%760,000</t>
+          <t>3.27%9,785,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>760000</v>
+        <v>9785000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>+0.55%1840</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1830</v>
+        <v>1840</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.14%2,880,000</t>
+          <t>3.25%2,880,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+5.65%7200</t>
+          <t>-1.46%7095</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+5.65%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>7200</v>
+        <v>7095</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.01%700,000</t>
+          <t>3.05%700,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>-4.24%2035</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2125</v>
+        <v>2035</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.92%2,307,000</t>
+          <t>2.88%2,307,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.64%621</t>
+          <t>-5.96%584</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>621</v>
+        <v>584</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.59%7,000,000</t>
+          <t>2.51%7,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.59%</t>
+          <t>2.51%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:30</t>
+          <t>2026-08-31 19:30:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.64%899</t>
+          <t>+1.41%6100</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.64%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>899</v>
+        <v>6100</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.44%4,550,000</t>
+          <t>2.43%650,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>4550000</v>
+        <v>650000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.6%6015</t>
+          <t>-0.81%1230</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6015</v>
+        <v>1230</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.33%650,000</t>
+          <t>1.99%2,640,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.33%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>650000</v>
+        <v>2640000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.25%1240</t>
+          <t>-3.98%2170</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1240</v>
+        <v>2170</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.95%2,640,000</t>
+          <t>1.72%1,293,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>1.72%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2640000</v>
+        <v>1293000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>-8.9%819</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2260</v>
+        <v>819</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.74%1,293,000</t>
+          <t>1.71%3,400,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1293000</v>
+        <v>3400000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3.11%1490</t>
+          <t>-3.69%1435</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1490</v>
+        <v>1435</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.69%1,900,000</t>
+          <t>1.67%1,900,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.46%972</t>
+          <t>+9.98%242.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>972</v>
+        <v>242.5</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.62%2,800,000</t>
+          <t>1.64%11,000,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.64%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2800000</v>
+        <v>11000000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+5.39%2345</t>
+          <t>-6.17%912</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>-6.17%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2345</v>
+        <v>912</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.47%1,050,000</t>
+          <t>1.57%2,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1050000</v>
+        <v>2800000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-3.08%220.5</t>
+          <t>-1.71%2305</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>-1.71%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>220.5</v>
+        <v>2305</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.45%11,000,000</t>
+          <t>1.48%1,050,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>11000000</v>
+        <v>1050000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+2.12%15630</t>
+          <t>+2.78%16065</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>15630</v>
+        <v>16065</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.39%149,500</t>
+          <t>1.47%149,500</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.44%1265</t>
+          <t>+0.55%182.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1265</v>
+        <v>182.5</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.31%1,737,000</t>
+          <t>1.34%12,000,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1737000</v>
+        <v>12000000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.42%181.5</t>
+          <t>-7.11%1175</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-7.11%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>181.5</v>
+        <v>1175</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.30%12,000,000</t>
+          <t>1.25%1,737,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>12000000</v>
+        <v>1737000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.01%2010</t>
+          <t>-2.49%1960</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2010</v>
+        <v>1960</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+3.61%287</t>
+          <t>-3.48%277</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>-3.48%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.92%5,360,000</t>
+          <t>0.91%5,360,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+2.29%6490</t>
+          <t>-1.19%250</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6490</v>
+        <v>250</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.50%130,000</t>
+          <t>0.49%3,200,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>130000</v>
+        <v>3200000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.63%400</t>
+          <t>-3.37%386.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>-3.37%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>400</v>
+        <v>386.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.48%2,000,000</t>
+          <t>0.47%2,000,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:32</t>
+          <t>2026-08-31 19:30:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.4%253</t>
+          <t>-9.71%5860</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-9.71%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>253</v>
+        <v>5860</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.48%3,200,000</t>
+          <t>0.47%130,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>3200000</v>
+        <v>130000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.45%749</t>
+          <t>-3.34%724</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.45%</t>
+          <t>-3.34%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>749</v>
+        <v>724</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.78%126.5</t>
+          <t>-0.4%126</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>126.5</v>
+        <v>126</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.34%4,500,000</t>
+          <t>0.35%4,500,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.28%14300</t>
+          <t>-0.84%14180</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.84%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14300</v>
+        <v>14180</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+6.77%1735</t>
+          <t>-2.59%1690</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+6.77%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1735</v>
+        <v>1690</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.25%1615</t>
+          <t>+0.93%1630</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1615</v>
+        <v>1630</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+9.92%543</t>
+          <t>-0.55%540</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.19%600,000</t>
+          <t>0.20%600,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,25 +2700,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0%1075</t>
+          <t>+1.73%646</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1075</v>
+        <v>646</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.16%250,000</t>
+          <t>0.16%400,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>250000</v>
+        <v>400000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+9.86%635</t>
+          <t>-1.4%1060</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+9.86%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>635</v>
+        <v>1060</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.15%400,000</t>
+          <t>0.16%250,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>400000</v>
+        <v>250000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+2.51%77.7</t>
+          <t>+6.18%82.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.51%</t>
+          <t>+6.18%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>77.7</v>
+        <v>82.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.13%2,800,000</t>
+          <t>0.14%2,800,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+0.72%695</t>
+          <t>-1.73%683</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.12%300,000</t>
+          <t>0.13%300,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,34 +2944,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+7.06%235</t>
+          <t>+9.91%477</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+7.06%</t>
+          <t>+9.91%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>235</v>
+        <v>477</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.10%700,000</t>
+          <t>0.11%386,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>700000</v>
+        <v>386000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,34 +3005,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.02%584</t>
+          <t>-2.98%228</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>584</v>
+        <v>228</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.08%220,000</t>
+          <t>0.10%700,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>220000</v>
+        <v>700000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.82%247</t>
+          <t>-1.03%578</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>247</v>
+        <v>578</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.05%350,000</t>
+          <t>0.08%220,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>350000</v>
+        <v>220000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.23%434</t>
+          <t>-4.81%257</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-4.81%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>434</v>
+        <v>257</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.05%200,000</t>
+          <t>0.08%500,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>200000</v>
+        <v>500000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:33</t>
+          <t>2026-08-31 19:30:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.23%2150</t>
+          <t>-1.21%244</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2150</v>
+        <v>244</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.05%350,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>1000</v>
+        <v>350000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:34</t>
+          <t>2026-08-31 19:30:32</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,21 +3249,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.01%492.5</t>
+          <t>+0.7%2165</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.01%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>492.5</v>
+        <v>2165</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:34</t>
+          <t>2026-08-31 19:30:32</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.73%480.5</t>
+          <t>-1.52%485</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>480.5</v>
+        <v>485</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:34</t>
+          <t>2026-08-31 19:30:32</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2049上銀</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.53%354</t>
+          <t>+4.06%500</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.53%</t>
+          <t>+4.06%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>354</v>
+        <v>500</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:34</t>
+          <t>2026-08-31 19:30:32</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>2049上銀</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.32%153</t>
+          <t>-1.13%350</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>153</v>
+        <v>350</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 00:38:34</t>
+          <t>2026-08-31 19:30:32</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+5.12%154</t>
+          <t>-0.98%151.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+5.12%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>154</v>
+        <v>151.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3528,6 +3528,67 @@
         </is>
       </c>
       <c r="M51" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:30:32</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2481強茂</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-1.95%151</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-1.95%</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>151</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-08-31_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:28</t>
+          <t>2026-08-31 22:13:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:30</t>
+          <t>2026-08-31 22:13:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:31</t>
+          <t>2026-08-31 22:13:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:32</t>
+          <t>2026-08-31 22:13:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:32</t>
+          <t>2026-08-31 22:13:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:32</t>
+          <t>2026-08-31 22:13:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:32</t>
+          <t>2026-08-31 22:13:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:32</t>
+          <t>2026-08-31 22:13:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-31 19:30:32</t>
+          <t>2026-08-31 22:13:41</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-08-31_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:37</t>
+          <t>2026-08-31 22:22:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:38</t>
+          <t>2026-08-31 22:22:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:39</t>
+          <t>2026-08-31 22:22:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:41</t>
+          <t>2026-08-31 22:22:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:41</t>
+          <t>2026-08-31 22:22:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:41</t>
+          <t>2026-08-31 22:22:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:41</t>
+          <t>2026-08-31 22:22:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:41</t>
+          <t>2026-08-31 22:22:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:41</t>
+          <t>2026-08-31 22:22:36</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
